--- a/basedatos_partidas/salida/descompuestos/CT-04-01-090.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-04-01-090.xlsx
@@ -539,10 +539,10 @@
         <v>0.22</v>
       </c>
       <c r="G10" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H10" t="n">
-        <v>27.5</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>29.7</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="12">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>77.95999999999999</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="17">
@@ -932,10 +932,10 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>102.54</v>
+        <v>97.7</v>
       </c>
       <c r="H29" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="30">
@@ -951,7 +951,7 @@
       </c>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="5" t="n">
-        <v>103.57</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-04-01-090.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-04-01-090.xlsx
@@ -591,10 +591,10 @@
         <v>0.45</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H12" t="n">
-        <v>9.9</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="13">
@@ -617,10 +617,10 @@
         <v>0.3</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -643,10 +643,10 @@
         <v>1.1</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>6.16</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="15">
@@ -669,10 +669,10 @@
         <v>0.28</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="16">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>73.12</v>
+        <v>107.78</v>
       </c>
     </row>
     <row r="17">
@@ -932,10 +932,10 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>97.7</v>
+        <v>132.36</v>
       </c>
       <c r="H29" t="n">
-        <v>0.98</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="30">
@@ -951,7 +951,7 @@
       </c>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="5" t="n">
-        <v>98.68000000000001</v>
+        <v>133.68</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-04-01-090.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-04-01-090.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 04 Fundaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Bases y zapatas</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
